--- a/data/output/2025/evaluasi_81.xlsx
+++ b/data/output/2025/evaluasi_81.xlsx
@@ -18,6 +18,7 @@
     <sheet name="8109" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="8171" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="8172" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="8104" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -817,7 +818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -989,6 +990,258 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Ambon</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.569649732396524</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Ambon</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>29.05102706537638</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Ambon</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.63603241078838</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Ambon</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-6.942398386604746</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Ambon</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-3.881889336951246</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Ambon</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.6666101800982656</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Ambon</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.1818484085723903</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Ambon</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.3700000000000121</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8171</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Ambon</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.3285216604998116</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1316,640 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>31.04313549294402</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.01593737055486</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8.428551508961613</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-4.357130410126954</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.007462366530981</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.454368062518555</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.732908390416886</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5.198102783616952</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.240860085721085</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.9305345432553908</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8172</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Tual</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.6505180083767852</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>8104</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-5.571649220286416</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>8104</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>37.06431560699283</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8104</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.82841348714222</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8104</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.490685358504517</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8104</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>19.68399494661387</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8104</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2400966386109218</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8104</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.032649017058223</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8104</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.468096264754773</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8104</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2184677436496469</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8104</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.4236113669898238</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1333,6 +2220,286 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8101</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Tanimbar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>32.11932146791143</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8101</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Tanimbar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>16.78058778285284</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8101</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Tanimbar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>26.38481236212162</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8101</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Tanimbar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.22880543787943</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8101</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Tanimbar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.28404163345288</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q4-25_prov vs c-to-c_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8101</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Tanimbar</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.1578049980535383</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8101</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Tanimbar</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3.068564739671495</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8101</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Tanimbar</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-2.60588154253497</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>8101</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Tanimbar</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-1.999419348228897</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>8101</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Tanimbar</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.5777680009003858</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1347,7 +2514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1463,6 +2630,342 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8.394325679125089</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.932758723000012</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.49999999999965</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.8993502577064</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8.277608023311975</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1409917752657244</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.300895910891799</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-3.426487153507192</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.516587248304318</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.252881043766197</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.3125336697714554</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8108</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Barat Daya</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.1714037559258119</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1477,7 +2980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1621,6 +3124,230 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.338674651668065</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6.533905097577689</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1068702614793902</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.542076560224199</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.983684959259728</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.944942347200324</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.4327996830400327</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8102</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tenggara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.3256728097265828</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1635,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1751,6 +3478,258 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8103</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tengah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7.674880774196188</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8103</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tengah</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.092686084589507</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8103</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tengah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.578021631952019</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8103</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tengah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7031405565609806</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8103</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tengah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.386438218833666</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8103</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1866779513563159</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8103</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tengah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.19788115384007</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8103</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.89459655411649</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8103</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Maluku Tengah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.02736548520333726</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1765,7 +3744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,6 +3860,286 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8105</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Aru</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.596505220347359</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8105</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Aru</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.64197966116742</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8105</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Aru</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-6.866636689355728</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8105</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Aru</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.464741551598361</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8105</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Aru</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9081119365123576</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8105</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Aru</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.04811686082254957</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8105</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Aru</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.8253499715167284</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8105</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Aru</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-2.02847739271251</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8105</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Aru</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.7253379969298914</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8105</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Aru</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.5939513233357894</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1895,7 +4154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2011,6 +4270,230 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8106</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.69367603316084</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8106</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.49602292894138</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8106</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-6.822545899198865</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8106</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5993396164787607</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8106</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.3916683550720306</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8106</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Barat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.075769479818888</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8106</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Barat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.4300063221292602</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8106</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Barat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.5011678063650933</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2025,7 +4508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2169,6 +4652,230 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8107</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.15571584280589</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8107</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8.733769337901157</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8107</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.243227358963662</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8107</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.03693026669199841</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8107</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.693411796450894</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8107</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Timur</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.471607955046743</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8107</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Timur</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.08418919576797</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8107</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Seram Bagian Timur</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.6129782240066413</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2183,7 +4890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2330,6 +5037,258 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6.502704712370501</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9.019491380099307</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-9.364711756399265</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6.69915103664042</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.667447927013938</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.7414424612591377</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.4762777028062612</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.2033289555025494</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>8109</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Buru Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.4163485151390487</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
